--- a/outputs/Block2_2026_Fold_Summary_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Summary_v12.xlsx
@@ -453,28 +453,28 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="C2">
-        <v>7.056379232505655</v>
+        <v>7.633567303420703</v>
       </c>
       <c r="D2">
-        <v>5.329070518200751E-15</v>
+        <v>8.881784197001252E-16</v>
       </c>
       <c r="E2">
-        <v>0.01255022013825051</v>
+        <v>0.01357678590413057</v>
       </c>
       <c r="F2">
-        <v>0.02245051628937196</v>
+        <v>0.02428689295807753</v>
       </c>
       <c r="G2">
-        <v>7.036027088036134</v>
+        <v>7.611550422034657</v>
       </c>
       <c r="H2">
-        <v>7.065101580135458</v>
+        <v>7.643003109729013</v>
       </c>
       <c r="I2">
-        <v>0.02907449209932444</v>
+        <v>0.0314526876943555</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -485,28 +485,28 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C3">
-        <v>218</v>
+        <v>220.6</v>
       </c>
       <c r="D3">
-        <v>-1</v>
+        <v>-2.400000000000006</v>
       </c>
       <c r="E3">
-        <v>9.273618495495704</v>
+        <v>10.11434624679223</v>
       </c>
       <c r="F3">
-        <v>16.58915308266218</v>
+        <v>18.09309260463783</v>
       </c>
       <c r="G3">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H3">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
         <v>13</v>
@@ -520,16 +520,16 @@
         <v>50</v>
       </c>
       <c r="C4">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="D4">
-        <v>-1.399999999999999</v>
+        <v>-1.200000000000003</v>
       </c>
       <c r="E4">
-        <v>1.816590212458495</v>
+        <v>1.788854381999832</v>
       </c>
       <c r="F4">
-        <v>3.249615361854384</v>
+        <v>3.2</v>
       </c>
       <c r="G4">
         <v>46</v>

--- a/outputs/Block2_2026_Fold_Summary_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Summary_v12.xlsx
@@ -453,28 +453,28 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>7.633567303420702</v>
+        <v>8.480204489886656</v>
       </c>
       <c r="C2">
-        <v>7.633567303420703</v>
+        <v>8.480204489886651</v>
       </c>
       <c r="D2">
-        <v>8.881784197001252E-16</v>
+        <v>-5.329070518200751E-15</v>
       </c>
       <c r="E2">
-        <v>0.01357678590413057</v>
+        <v>0.01508258409287546</v>
       </c>
       <c r="F2">
-        <v>0.02428689295807753</v>
+        <v>0.02698054664642122</v>
       </c>
       <c r="G2">
-        <v>7.611550422034657</v>
+        <v>8.455745721271402</v>
       </c>
       <c r="H2">
-        <v>7.643003109729013</v>
+        <v>8.490686819293192</v>
       </c>
       <c r="I2">
-        <v>0.0314526876943555</v>
+        <v>0.03494109802178968</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
@@ -485,28 +485,28 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="C3">
-        <v>220.6</v>
+        <v>215</v>
       </c>
       <c r="D3">
-        <v>-2.400000000000006</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>10.11434624679223</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>18.09309260463783</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H3">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="I3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J3" t="s">
         <v>13</v>
@@ -517,28 +517,28 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C4">
-        <v>48.8</v>
+        <v>47</v>
       </c>
       <c r="D4">
-        <v>-1.200000000000003</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>1.788854381999832</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4" t="s">
         <v>13</v>

--- a/outputs/Block2_2026_Fold_Summary_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Summary_v12.xlsx
@@ -453,28 +453,28 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>8.480204489886656</v>
+        <v>8.465151985799857</v>
       </c>
       <c r="C2">
-        <v>8.480204489886651</v>
+        <v>8.465151985799853</v>
       </c>
       <c r="D2">
-        <v>-5.329070518200751E-15</v>
+        <v>-3.552713678800501E-15</v>
       </c>
       <c r="E2">
-        <v>0.01508258409287546</v>
+        <v>0.01505581225512342</v>
       </c>
       <c r="F2">
-        <v>0.02698054664642122</v>
+        <v>0.0269326557271443</v>
       </c>
       <c r="G2">
-        <v>8.455745721271402</v>
+        <v>8.44073663190591</v>
       </c>
       <c r="H2">
-        <v>8.490686819293192</v>
+        <v>8.47561570889726</v>
       </c>
       <c r="I2">
-        <v>0.03494109802178968</v>
+        <v>0.03487907699135029</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>

--- a/outputs/Block2_2026_Fold_Summary_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Summary_v12.xlsx
@@ -453,28 +453,28 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>8.465151985799857</v>
+        <v>8.20605605826527</v>
       </c>
       <c r="C2">
-        <v>8.465151985799853</v>
+        <v>8.206056058265274</v>
       </c>
       <c r="D2">
-        <v>-3.552713678800501E-15</v>
+        <v>3.552713678800501E-15</v>
       </c>
       <c r="E2">
-        <v>0.01505581225512342</v>
+        <v>0.01459499363691642</v>
       </c>
       <c r="F2">
-        <v>0.0269326557271443</v>
+        <v>0.0261083183226576</v>
       </c>
       <c r="G2">
-        <v>8.44073663190591</v>
+        <v>8.182387993820333</v>
       </c>
       <c r="H2">
-        <v>8.47561570889726</v>
+        <v>8.216199514455964</v>
       </c>
       <c r="I2">
-        <v>0.03487907699135029</v>
+        <v>0.03381152063563064</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>

--- a/outputs/Block2_2026_Fold_Summary_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Summary_v12.xlsx
@@ -453,28 +453,28 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>8.20605605826527</v>
+        <v>8.833213186813193</v>
       </c>
       <c r="C2">
-        <v>8.206056058265274</v>
+        <v>8.833213186813191</v>
       </c>
       <c r="D2">
-        <v>3.552713678800501E-15</v>
+        <v>-1.77635683940025E-15</v>
       </c>
       <c r="E2">
-        <v>0.01459499363691642</v>
+        <v>0.01571043255611215</v>
       </c>
       <c r="F2">
-        <v>0.0261083183226576</v>
+        <v>0.02810367612111404</v>
       </c>
       <c r="G2">
-        <v>8.182387993820333</v>
+        <v>8.807736263736265</v>
       </c>
       <c r="H2">
-        <v>8.216199514455964</v>
+        <v>8.844131868131877</v>
       </c>
       <c r="I2">
-        <v>0.03381152063563064</v>
+        <v>0.03639560439561151</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>

--- a/outputs/Block2_2026_Fold_Summary_v12.xlsx
+++ b/outputs/Block2_2026_Fold_Summary_v12.xlsx
@@ -453,28 +453,28 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>8.833213186813193</v>
+        <v>8.529156311314573</v>
       </c>
       <c r="C2">
-        <v>8.833213186813191</v>
+        <v>8.529156311314569</v>
       </c>
       <c r="D2">
-        <v>-1.77635683940025E-15</v>
+        <v>-3.552713678800501E-15</v>
       </c>
       <c r="E2">
-        <v>0.01571043255611215</v>
+        <v>0.01516964802677459</v>
       </c>
       <c r="F2">
-        <v>0.02810367612111404</v>
+        <v>0.02713629134609082</v>
       </c>
       <c r="G2">
-        <v>8.807736263736265</v>
+        <v>8.504556354916055</v>
       </c>
       <c r="H2">
-        <v>8.844131868131877</v>
+        <v>8.53969914977108</v>
       </c>
       <c r="I2">
-        <v>0.03639560439561151</v>
+        <v>0.03514279485502492</v>
       </c>
       <c r="J2" t="s">
         <v>13</v>
